--- a/pretty_graph_schema.xlsx
+++ b/pretty_graph_schema.xlsx
@@ -1,31 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anees\Documents\R_Workspace\ns_gender_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blaze\Documents\R Workspace\ns_gender_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A845443-3898-4483-8995-DC604801AC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B63FD8-50CE-4BD1-B322-8F7E281D8E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="34">
   <si>
     <t>type</t>
   </si>
@@ -33,30 +66,116 @@
     <t>abs_rel</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>FA_func_LA_abs</t>
-  </si>
-  <si>
-    <t>FA_func_LA_rel</t>
-  </si>
-  <si>
     <t>split_sum</t>
   </si>
   <si>
     <t>fa_la</t>
   </si>
   <si>
-    <t>measure</t>
+    <t>base_df</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>changed_y</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>shape_filt</t>
+  </si>
+  <si>
+    <t>fa</t>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>time_auth_prod</t>
+  </si>
+  <si>
+    <t>scatter</t>
+  </si>
+  <si>
+    <t>la</t>
+  </si>
+  <si>
+    <t>abs</t>
+  </si>
+  <si>
+    <t>rel</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>subtype</t>
+  </si>
+  <si>
+    <t>auth_</t>
+  </si>
+  <si>
+    <t>prod_</t>
+  </si>
+  <si>
+    <t>art_</t>
+  </si>
+  <si>
+    <t>scatter_prod_</t>
+  </si>
+  <si>
+    <t>fa_sum</t>
+  </si>
+  <si>
+    <t>la_sum</t>
+  </si>
+  <si>
+    <t>Year of Publication</t>
+  </si>
+  <si>
+    <t>Number of Articles</t>
+  </si>
+  <si>
+    <t>scatter_auth_</t>
+  </si>
+  <si>
+    <t>plot_name</t>
+  </si>
+  <si>
+    <t>sep</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -72,7 +191,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -80,12 +199,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -366,44 +495,1254 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="2" width="16" customWidth="1"/>
     <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" customWidth="1"/>
+    <col min="11" max="11" width="27.28515625" customWidth="1"/>
+    <col min="12" max="12" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="str">
+        <f>_xlfn.CONCAT(B2:C2,"_",D2,"_",E2)</f>
+        <v>art_fa_abs_split</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2">_xlfn.SWITCH(B2,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Articles</v>
+      </c>
+      <c r="K2" cm="1">
+        <f t="array" ref="K2">IF(D2="rel",_xlfn.SWITCH(J2,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" t="str">
+        <f>_xlfn.CONCAT(IF(B2="auth_","Unique ",),_xlfn.SWITCH(C2,"fa","First Author Gender","la", "Last Author Gender"))</f>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G19" si="0">_xlfn.CONCAT(B3:C3,"_",D3,"_",E3)</f>
+        <v>art_fa_abs_sum</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="str" cm="1">
+        <f t="array" ref="J3">_xlfn.SWITCH(B3,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Articles</v>
+      </c>
+      <c r="K3" cm="1">
+        <f t="array" ref="K3">IF(D3="rel",_xlfn.SWITCH(J3,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L31" si="1">_xlfn.CONCAT(IF(B3="auth_","Unique ",),_xlfn.SWITCH(C3,"fa","First Author Gender","la", "Last Author Gender"))</f>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="0"/>
+        <v>art_fa_rel_split</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="str" cm="1">
+        <f t="array" ref="J4">_xlfn.SWITCH(B4,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Articles</v>
+      </c>
+      <c r="K4" t="str" cm="1">
+        <f t="array" ref="K4">IF(D4="rel",_xlfn.SWITCH(J4,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>Proportion of Articles</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="0"/>
+        <v>art_la_abs_split</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="str" cm="1">
+        <f t="array" ref="J5">_xlfn.SWITCH(B5,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Articles</v>
+      </c>
+      <c r="K5" cm="1">
+        <f t="array" ref="K5">IF(D5="rel",_xlfn.SWITCH(J5,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="0"/>
+        <v>art_la_abs_sum</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="str" cm="1">
+        <f t="array" ref="J6">_xlfn.SWITCH(B6,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Articles</v>
+      </c>
+      <c r="K6" cm="1">
+        <f t="array" ref="K6">IF(D6="rel",_xlfn.SWITCH(J6,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v>art_la_rel_split</v>
+      </c>
+      <c r="H7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" t="str" cm="1">
+        <f t="array" ref="J7">_xlfn.SWITCH(B7,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Articles</v>
+      </c>
+      <c r="K7" t="str" cm="1">
+        <f t="array" ref="K7">IF(D7="rel",_xlfn.SWITCH(J7,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>Proportion of Articles</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>auth_fa_abs_split</v>
+      </c>
+      <c r="H8" t="str">
+        <f>_xlfn.CONCAT(B8:C8)</f>
+        <v>auth_fa</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" t="str" cm="1">
+        <f t="array" ref="J8">_xlfn.SWITCH(B8,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="K8" cm="1">
+        <f t="array" ref="K8">IF(D8="rel",_xlfn.SWITCH(J8,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique First Author Gender</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>auth_fa_abs_sum</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" ref="H9:H19" si="2">_xlfn.CONCAT(B9:C9)</f>
+        <v>auth_fa</v>
+      </c>
+      <c r="I9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" t="str" cm="1">
+        <f t="array" ref="J9">_xlfn.SWITCH(B9,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="K9" cm="1">
+        <f t="array" ref="K9">IF(D9="rel",_xlfn.SWITCH(J9,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique First Author Gender</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>auth_fa_rel_split</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="2"/>
+        <v>auth_fa</v>
+      </c>
+      <c r="I10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" t="str" cm="1">
+        <f t="array" ref="J10">_xlfn.SWITCH(B10,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="K10" t="str" cm="1">
+        <f t="array" ref="K10">IF(D10="rel",_xlfn.SWITCH(J10,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>Proportion of Unique Authors</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique First Author Gender</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="0"/>
+        <v>auth_la_abs_split</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="2"/>
+        <v>auth_la</v>
+      </c>
+      <c r="I11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" t="str" cm="1">
+        <f t="array" ref="J11">_xlfn.SWITCH(B11,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="K11" cm="1">
+        <f t="array" ref="K11">IF(D11="rel",_xlfn.SWITCH(J11,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique Last Author Gender</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v>auth_la_abs_sum</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="2"/>
+        <v>auth_la</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" t="str" cm="1">
+        <f t="array" ref="J12">_xlfn.SWITCH(B12,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="K12" cm="1">
+        <f t="array" ref="K12">IF(D12="rel",_xlfn.SWITCH(J12,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique Last Author Gender</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="0"/>
+        <v>auth_la_rel_split</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="2"/>
+        <v>auth_la</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="str" cm="1">
+        <f t="array" ref="J13">_xlfn.SWITCH(B13,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="K13" t="str" cm="1">
+        <f t="array" ref="K13">IF(D13="rel",_xlfn.SWITCH(J13,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>Proportion of Unique Authors</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique Last Author Gender</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="0"/>
+        <v>prod_fa_abs_split</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="2"/>
+        <v>prod_fa</v>
+      </c>
+      <c r="I14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" t="str" cm="1">
+        <f t="array" ref="J14">_xlfn.SWITCH(B14,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="K14" cm="1">
+        <f t="array" ref="K14">IF(D14="rel",_xlfn.SWITCH(J14,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="0"/>
+        <v>prod_fa_abs_sum</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="2"/>
+        <v>prod_fa</v>
+      </c>
+      <c r="I15" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" t="str" cm="1">
+        <f t="array" ref="J15">_xlfn.SWITCH(B15,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="K15" cm="1">
+        <f t="array" ref="K15">IF(D15="rel",_xlfn.SWITCH(J15,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="0"/>
+        <v>prod_fa_rel_split</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="2"/>
+        <v>prod_fa</v>
+      </c>
+      <c r="I16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" t="str" cm="1">
+        <f t="array" ref="J16">_xlfn.SWITCH(B16,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="K16" t="str" cm="1">
+        <f t="array" ref="K16">IF(D16="rel",_xlfn.SWITCH(J16,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>Productivity Ratio</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="0"/>
+        <v>prod_la_abs_split</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="2"/>
+        <v>prod_la</v>
+      </c>
+      <c r="I17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" t="str" cm="1">
+        <f t="array" ref="J17">_xlfn.SWITCH(B17,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="K17" cm="1">
+        <f t="array" ref="K17">IF(D17="rel",_xlfn.SWITCH(J17,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="0"/>
+        <v>prod_la_abs_sum</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="2"/>
+        <v>prod_la</v>
+      </c>
+      <c r="I18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" t="str" cm="1">
+        <f t="array" ref="J18">_xlfn.SWITCH(B18,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="K18" cm="1">
+        <f t="array" ref="K18">IF(D18="rel",_xlfn.SWITCH(J18,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="0"/>
+        <v>prod_la_rel_split</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="2"/>
+        <v>prod_la</v>
+      </c>
+      <c r="I19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" t="str" cm="1">
+        <f t="array" ref="J19">_xlfn.SWITCH(B19,"art_","Number of Articles","auth_","Number of Unique Authors", "prod_", "Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="K19" t="str" cm="1">
+        <f t="array" ref="K19">IF(D19="rel",_xlfn.SWITCH(J19,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>Productivity Ratio</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" t="str">
+        <f>_xlfn.CONCAT(B20:C20,"_",F20)</f>
+        <v>scatter_auth_fa_Female</v>
+      </c>
+      <c r="H20" t="str">
+        <f>_xlfn.CONCAT(C20,"_merged")</f>
+        <v>fa_merged</v>
+      </c>
+      <c r="I20" t="str" cm="1">
+        <f t="array" ref="I20">_xlfn.SWITCH(B20,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="J20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" cm="1">
+        <f t="array" ref="K20">IF(D20="rel",_xlfn.SWITCH(J20,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" ref="G21:G31" si="3">_xlfn.CONCAT(B21:C21,"_",F21)</f>
+        <v>scatter_auth_fa_Male</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" ref="H21:H31" si="4">_xlfn.CONCAT(C21,"_merged")</f>
+        <v>fa_merged</v>
+      </c>
+      <c r="I21" t="str" cm="1">
+        <f t="array" ref="I21">_xlfn.SWITCH(B21,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="J21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" cm="1">
+        <f t="array" ref="K21">IF(D21="rel",_xlfn.SWITCH(J21,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_auth_fa_Sum</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="4"/>
+        <v>fa_merged</v>
+      </c>
+      <c r="I22" t="str" cm="1">
+        <f t="array" ref="I22">_xlfn.SWITCH(B22,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="J22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" cm="1">
+        <f t="array" ref="K22">IF(D22="rel",_xlfn.SWITCH(J22,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_auth_la_Female</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="4"/>
+        <v>la_merged</v>
+      </c>
+      <c r="I23" t="str" cm="1">
+        <f t="array" ref="I23">_xlfn.SWITCH(B23,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="J23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" cm="1">
+        <f t="array" ref="K23">IF(D23="rel",_xlfn.SWITCH(J23,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_auth_la_Male</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="4"/>
+        <v>la_merged</v>
+      </c>
+      <c r="I24" t="str" cm="1">
+        <f t="array" ref="I24">_xlfn.SWITCH(B24,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="J24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" cm="1">
+        <f t="array" ref="K24">IF(D24="rel",_xlfn.SWITCH(J24,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_auth_la_Sum</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="4"/>
+        <v>la_merged</v>
+      </c>
+      <c r="I25" t="str" cm="1">
+        <f t="array" ref="I25">_xlfn.SWITCH(B25,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Number of Unique Authors</v>
+      </c>
+      <c r="J25" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" cm="1">
+        <f t="array" ref="K25">IF(D25="rel",_xlfn.SWITCH(J25,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_prod_fa_Female</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="4"/>
+        <v>fa_merged</v>
+      </c>
+      <c r="I26" t="str" cm="1">
+        <f t="array" ref="I26">_xlfn.SWITCH(B26,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" cm="1">
+        <f t="array" ref="K26">IF(D26="rel",_xlfn.SWITCH(J26,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L26" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_prod_fa_Male</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="4"/>
+        <v>fa_merged</v>
+      </c>
+      <c r="I27" t="str" cm="1">
+        <f t="array" ref="I27">_xlfn.SWITCH(B27,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="J27" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" cm="1">
+        <f t="array" ref="K27">IF(D27="rel",_xlfn.SWITCH(J27,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_prod_fa_Sum</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="4"/>
+        <v>fa_merged</v>
+      </c>
+      <c r="I28" t="str" cm="1">
+        <f t="array" ref="I28">_xlfn.SWITCH(B28,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="J28" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" cm="1">
+        <f t="array" ref="K28">IF(D28="rel",_xlfn.SWITCH(J28,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="1"/>
+        <v>First Author Gender</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_prod_la_Female</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="4"/>
+        <v>la_merged</v>
+      </c>
+      <c r="I29" t="str" cm="1">
+        <f t="array" ref="I29">_xlfn.SWITCH(B29,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="J29" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" cm="1">
+        <f t="array" ref="K29">IF(D29="rel",_xlfn.SWITCH(J29,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_prod_la_Male</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="4"/>
+        <v>la_merged</v>
+      </c>
+      <c r="I30" t="str" cm="1">
+        <f t="array" ref="I30">_xlfn.SWITCH(B30,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="J30" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" cm="1">
+        <f t="array" ref="K30">IF(D30="rel",_xlfn.SWITCH(J30,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="3"/>
+        <v>scatter_prod_la_Sum</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="4"/>
+        <v>la_merged</v>
+      </c>
+      <c r="I31" t="str" cm="1">
+        <f t="array" ref="I31">_xlfn.SWITCH(B31,"scatter_auth_","Number of Unique Authors","scatter_prod_","Mean Productivity")</f>
+        <v>Mean Productivity</v>
+      </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" cm="1">
+        <f t="array" ref="K31">IF(D31="rel",_xlfn.SWITCH(J31,"Number of Articles","Proportion of Articles", "Number of Unique Authors","Proportion of Unique Authors", "Mean Productivity","Productivity Ratio"),)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="1"/>
+        <v>Last Author Gender</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>